--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2019_metropolitana.xlsx
@@ -177,18 +177,18 @@
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colina</t>
   </si>
   <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puente Alto</t>
   </si>
   <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Pedro</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:14</t>
+    <t xml:space="preserve">2026-09-10 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1430,7 +1430,7 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13301</v>
+        <v>13603</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1456,7 +1456,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13201</v>
+        <v>13301</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -1469,7 +1469,7 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13603</v>
+        <v>13201</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:18</t>
+    <t xml:space="preserve">2026-09-18 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
